--- a/Documents/Product Catalog/Kids Bed.xlsx
+++ b/Documents/Product Catalog/Kids Bed.xlsx
@@ -1375,7 +1375,7 @@
         <v/>
       </c>
       <c r="L6" s="12" t="n">
-        <v>19350</v>
+        <v>17500</v>
       </c>
       <c r="M6" s="10" t="n">
         <v>0.1</v>
@@ -1507,7 +1507,7 @@
         <v/>
       </c>
       <c r="L7" s="12" t="n">
-        <v>19800</v>
+        <v>20500</v>
       </c>
       <c r="M7" s="10" t="n">
         <v>0.1</v>
@@ -1639,7 +1639,7 @@
         <v/>
       </c>
       <c r="L8" s="12" t="n">
-        <v>18900</v>
+        <v>18300</v>
       </c>
       <c r="M8" s="10" t="n">
         <v>0.1</v>
@@ -1772,7 +1772,7 @@
         <v/>
       </c>
       <c r="L9" s="12" t="n">
-        <v>21600</v>
+        <v>20500</v>
       </c>
       <c r="M9" s="10" t="n">
         <v>0.1</v>
@@ -1906,7 +1906,7 @@
         <v/>
       </c>
       <c r="L10" s="12" t="n">
-        <v>20700</v>
+        <v>18200</v>
       </c>
       <c r="M10" s="10" t="n">
         <v>0.1</v>
